--- a/AAII_Financials/Quarterly/QS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="92">
   <si>
     <t>QS</t>
   </si>
@@ -656,123 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
@@ -785,8 +786,11 @@
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -829,8 +833,8 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
@@ -877,8 +881,11 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -969,8 +976,11 @@
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1061,8 +1071,11 @@
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1095,80 +1108,81 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>81300</v>
+      </c>
+      <c r="E12" s="3">
         <v>84600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>111200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>82600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>86400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>95600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>105900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>96700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>96600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>83800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>96400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>88200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>86500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>76900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>77500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>79800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>65100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>61300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>46800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>39500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>35800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>29500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>65100</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1187,8 +1201,11 @@
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1279,41 +1296,44 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-24400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>9500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>14800</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>23000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>24500</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1323,15 +1343,15 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>5900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>7800</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1347,8 +1367,8 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1371,53 +1391,56 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E15" s="3">
         <v>14800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>13600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>19500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>18300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>18000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>12000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>10800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>11600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>10000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>9500</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1463,8 +1486,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1494,86 +1520,87 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>104900</v>
+      </c>
+      <c r="E17" s="3">
         <v>109200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>134900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>105500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>108800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>123600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>105700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>129900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>133400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>107400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>124600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>120900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>123500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>110000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>113400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>120700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>95900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>90700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>67100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>53800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>49600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>44700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>79400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>100</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1586,86 +1613,89 @@
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-104900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-109200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-134900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-105500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-108800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-123600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-105700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-129900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-133400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-107400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-124600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-120900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-123500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-110000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-113400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-120700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-95900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-90700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-67100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-53800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-49600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-44700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-79400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-100</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1678,8 +1708,11 @@
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1712,85 +1745,86 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-2500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
-        <v>-500</v>
-      </c>
       <c r="H20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>69500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>130800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-30400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1580100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
+      <c r="AB20" s="3">
+        <v>0</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
@@ -1804,77 +1838,80 @@
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-91300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-94400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-118800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-91600</v>
       </c>
-      <c r="G21" s="3">
-        <v>-88900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-89000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-105200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-84000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-115300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-120400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-95600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-114400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-108800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-113200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-100800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-99200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-108600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-88400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-85000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-64200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>19000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>84700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-72900</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1896,8 +1933,11 @@
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1920,7 +1960,7 @@
         <v>500</v>
       </c>
       <c r="J22" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K22" s="3">
         <v>600</v>
@@ -1953,23 +1993,23 @@
         <v>600</v>
       </c>
       <c r="U22" s="3">
+        <v>600</v>
+      </c>
+      <c r="V22" s="3">
         <v>800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>200</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z22" s="3">
         <v>20800</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1988,86 +2028,89 @@
       <c r="AF22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-98000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-100800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-98600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-105800</v>
       </c>
-      <c r="G23" s="3">
-        <v>-114700</v>
-      </c>
       <c r="H23" s="3">
+        <v>-114900</v>
+      </c>
+      <c r="I23" s="3">
         <v>-114300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-114900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-119700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-123000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-120600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-113300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-110600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-116500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-104600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-109100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-117700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-94800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-90400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-67200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>15400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>81000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-75100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1680300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-100</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2080,32 +2123,35 @@
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>1500</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-300</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2124,8 +2170,8 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2172,8 +2218,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2264,86 +2313,89 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-98200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-100800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-100100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-105800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-114700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-114400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-114700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-119700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-123000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-120600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-113300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-110600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-116500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-104600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-109100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-117700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-94800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-90400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-67200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>15400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>81000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-75100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1680300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-100</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2356,86 +2408,89 @@
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-98200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-100800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-100100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-105800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-114700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-114400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-114700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-119600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-123000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-120600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-113400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-110600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-116500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-104600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-109100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-117700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-94800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-90400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-67200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>15400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>81000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-75100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1680300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-100</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2448,8 +2503,11 @@
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2540,8 +2598,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2632,8 +2693,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2724,8 +2788,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2816,85 +2883,88 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>2500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
-        <v>500</v>
-      </c>
       <c r="H32" s="3">
+        <v>300</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-69500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-130800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>30400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1580100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
+      <c r="AB32" s="3">
+        <v>0</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
@@ -2908,86 +2978,89 @@
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-98200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-100800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-100100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-105800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-114700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-114400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-114700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-119600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-123000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-120600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-113400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-110600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-116500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-104600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-109100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-117700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-94800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-90400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-67200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>15400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>81000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-75100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1680300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-100</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
@@ -3000,8 +3073,11 @@
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3092,86 +3168,89 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-98200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-100800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-100100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-105800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-114700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-114400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-114700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-119600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-123000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-120600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-113400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-110600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-116500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-104600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-109100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-117700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-94800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-90400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-67200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>15400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>81000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-75100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1680300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-100</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3184,91 +3263,94 @@
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3281,8 +3363,11 @@
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3315,8 +3400,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3349,86 +3435,87 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>132900</v>
+      </c>
+      <c r="E41" s="3">
         <v>145100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>230500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>225800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>172500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>153600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>140900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>174700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>196400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>192300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>142500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>250800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>232800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>241200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>235400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>298000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>343400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>283000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>320700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>346200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>402400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>762300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>113200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1700</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3441,80 +3528,83 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>726100</v>
+      </c>
+      <c r="E42" s="3">
         <v>759600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>740300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>777900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>625000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>706800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>769900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>666300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>741500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>817300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>928300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>876600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>676800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>741900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>826300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>857300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>924800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1065400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1127000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1197600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1165100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>771100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>884300</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,8 +3623,11 @@
       <c r="AF42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3580,8 +3673,8 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -3625,8 +3718,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3669,8 +3765,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3717,8 +3813,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3761,42 +3860,42 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>10600</v>
-      </c>
-      <c r="R45" s="3">
-        <v>10300</v>
       </c>
       <c r="S45" s="3">
         <v>10300</v>
       </c>
       <c r="T45" s="3">
+        <v>10300</v>
+      </c>
+      <c r="U45" s="3">
         <v>13800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>15800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>11600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>200</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3809,86 +3908,89 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>869100</v>
+      </c>
+      <c r="E46" s="3">
         <v>915900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>981600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1015500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>806200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>871500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>922300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>853700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>973500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1045000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1083500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1137600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>918600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>994600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1072300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1165600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1278400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1362200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1463400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1552300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1578200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1541900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1009200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2000</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3901,8 +4003,11 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3945,8 +4050,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3993,80 +4098,83 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>284000</v>
+      </c>
+      <c r="E48" s="3">
         <v>297300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>304900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>305600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>336000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>361200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>373700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>393200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>399200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>394700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>394200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>404900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>408800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>398200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>384700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>359200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>326700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>288600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>234000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>195900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>152700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>71600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>55400</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4085,8 +4193,11 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4177,8 +4288,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4269,8 +4383,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4361,86 +4478,89 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E52" s="3">
         <v>15900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>21600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>22100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>26100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>26300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>26400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>24100</v>
-      </c>
-      <c r="L52" s="3">
-        <v>24300</v>
       </c>
       <c r="M52" s="3">
         <v>24300</v>
       </c>
       <c r="N52" s="3">
+        <v>24300</v>
+      </c>
+      <c r="O52" s="3">
         <v>23300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>19900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>18300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>18400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>18300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>18400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>18100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>18200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>11100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>230100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>230000</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4453,8 +4573,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4545,86 +4668,89 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1168700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1229100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1308200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1343200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1168400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1258900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1322400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1272000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1396800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1464000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1502000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1565800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1347300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1411200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1475400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1543100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1623600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1669000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1715600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1759300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1743100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1616300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1066800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>231400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>232000</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4637,8 +4763,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4671,8 +4800,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4705,86 +4835,87 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E57" s="3">
         <v>7400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>15200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>21400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>23100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>22400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>14100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5400</v>
       </c>
-      <c r="Z57" s="3">
-        <v>0</v>
-      </c>
       <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="3">
         <v>300</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4797,85 +4928,88 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E58" s="3">
         <v>8500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1400</v>
-      </c>
-      <c r="R58" s="3">
-        <v>500</v>
       </c>
       <c r="S58" s="3">
         <v>500</v>
       </c>
       <c r="T58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>200</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z58" s="3">
-        <v>100</v>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA58" s="3">
         <v>100</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>3</v>
+      <c r="AB58" s="3">
+        <v>100</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>3</v>
@@ -4889,86 +5023,89 @@
       <c r="AF58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E59" s="3">
         <v>7200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12900</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>4000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3">
         <v>24000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>27700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>16200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>16400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>13700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>11500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>200</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4981,86 +5118,89 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>47200</v>
+      </c>
+      <c r="E60" s="3">
         <v>43800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>61500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>48000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>49200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>52300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>64900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>60700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>112400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>100700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>57100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>46300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>47700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>43500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>46800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>45400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>39800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>28000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>30600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>36300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>25300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>21400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>12400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>500</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5073,74 +5213,77 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>58400</v>
+      </c>
+      <c r="E61" s="3">
         <v>60700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>62800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>64900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>80100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>82500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>84800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>87100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>89200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>90600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>92700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>94700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>96800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>98800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>38000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>38700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>39300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>40000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>39400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>44100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>38700</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -5165,85 +5308,88 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E62" s="3">
         <v>15000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>14500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>14300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>15500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13600</v>
-      </c>
-      <c r="K62" s="3">
-        <v>13100</v>
       </c>
       <c r="L62" s="3">
         <v>13100</v>
       </c>
       <c r="M62" s="3">
+        <v>13100</v>
+      </c>
+      <c r="N62" s="3">
         <v>12000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>71000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>71200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>71600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>64600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>37100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>22100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>171000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>299400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11200</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>8100</v>
       </c>
       <c r="AA62" s="3">
         <v>8100</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
+      <c r="AB62" s="3">
+        <v>8100</v>
       </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
@@ -5257,8 +5403,11 @@
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5349,8 +5498,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5441,8 +5593,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5533,86 +5688,89 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>120800</v>
+      </c>
+      <c r="E66" s="3">
         <v>119400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>139200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>127500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>143600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>150300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>164500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>161400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>214700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>204300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>161800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>152700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>156300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>152500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>157600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>157000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>152400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>134300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>108800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>104200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>236600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>322400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>25300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8500</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5625,8 +5783,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5659,8 +5820,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5751,8 +5913,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5843,8 +6008,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5935,8 +6103,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6027,86 +6198,89 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3992600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3894400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3793600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3693500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3587600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3472900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3358500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3243900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-3124300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3001300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2880700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2767300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2656700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2540200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2435500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2326400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-2208800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2114000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2023600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1956400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1971700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-2052700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1395800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-100</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6119,8 +6293,11 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6211,8 +6388,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6303,8 +6483,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6395,86 +6578,89 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1048000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1109700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1169000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1215700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1024800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1108600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1157800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1110600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1180300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1257900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1338400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1411300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1189300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1257000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1317800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1386100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1471200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1534700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1606900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1655100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1506400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1293900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1041500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>222000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>223400</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6487,8 +6673,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6579,91 +6768,94 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6676,86 +6868,89 @@
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-98200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-100800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-100100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-105800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-114700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-114400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-114700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-119600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-123000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-120600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-113400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-110600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-116500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-104600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-109100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-117700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-94800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-90400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-67200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>15400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>81000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-75100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1680300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-100</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6768,8 +6963,11 @@
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6802,77 +7000,78 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E83" s="3">
         <v>20400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>20000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>17000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>14900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>12700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>10400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>9300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>8500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2200</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6888,14 +7087,17 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE83" s="3">
-        <v>0</v>
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6986,8 +7188,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7078,8 +7283,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7170,8 +7378,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7262,8 +7473,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7354,85 +7568,88 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-56700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-59500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-56200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-63700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-61800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-60700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-58700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-92800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-65200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-57900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-57500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-62600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-57700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-62300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-62900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-56400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-51300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-47400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-44600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-28900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-32900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-21500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-60600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-700</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
+      <c r="AB89" s="3">
+        <v>0</v>
       </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
@@ -7446,8 +7663,11 @@
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7480,77 +7700,78 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9900</v>
       </c>
-      <c r="G91" s="3">
-        <v>-8300</v>
-      </c>
       <c r="H91" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="I91" s="3">
         <v>-5800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-18000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-18900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-14100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-18000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-24700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-28000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-37800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-54100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-27600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-39300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-44800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-38700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-30400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-13300</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7566,14 +7787,17 @@
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7664,8 +7888,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7756,86 +7983,89 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-25700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>32000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-156400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>77300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>62000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-109100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>66100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>65300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>106500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-54000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-209000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>46400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>64100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>9600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>108200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>8400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>19400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-74700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-428400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>97800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-572600</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-230000</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7848,8 +8078,11 @@
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7882,8 +8115,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7926,8 +8160,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7974,8 +8208,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8066,8 +8303,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8158,8 +8398,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8250,86 +8493,89 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>27300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>270600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>11400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>133900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>5000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>290100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>6700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>46200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>110800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>572800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>722000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>231800</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8342,8 +8588,11 @@
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8386,8 +8635,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8434,86 +8683,89 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-85500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>50500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>18900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-33800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-21700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>49800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-108300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>18500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-62600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-45400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>60400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-37700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-18400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-57400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-350500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>649100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>88800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1700</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8524,6 +8776,9 @@
         <v>3</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
